--- a/results/Int All Data -0.9/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_8_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7151399713112037</v>
+        <v>0.7132031285446543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7136003043385697</v>
+        <v>0.7092950653176184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7113507467114333</v>
+        <v>0.7092950653176184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7025901934574188</v>
+        <v>0.708347497408585</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7047605253330448</v>
+        <v>0.7091376608509614</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7047605253330448</v>
+        <v>0.7076751255571105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7047209124572896</v>
+        <v>0.7086623063418993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7091001420479333</v>
+        <v>0.7105563951236027</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7059019694753998</v>
+        <v>0.7136357290688706</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7070069418510905</v>
+        <v>0.7166764971747468</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7098089856660722</v>
+        <v>0.7119438928113974</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7100862757963584</v>
+        <v>0.7119438928113974</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7082307528540466</v>
+        <v>0.7120627314386629</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7082307528540466</v>
+        <v>0.7102468213721063</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7085069959479693</v>
+        <v>0.7166442135535367</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7062167784087141</v>
+        <v>0.7147511718081969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7092950653176184</v>
+        <v>0.7147511718081969</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7092950653176184</v>
+        <v>0.7155402882142097</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7108743451660076</v>
+        <v>0.7158165313081324</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7100456158842396</v>
+        <v>0.7091085183388419</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7107951194144972</v>
+        <v>0.7084768063994863</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7102030203508968</v>
+        <v>0.7107659769023777</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.707636559717719</v>
+        <v>0.7171956527050185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7061750714602318</v>
+        <v>0.7143143831385264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.705385955054219</v>
+        <v>0.7147876435748614</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6842028388645938</v>
+        <v>0.7106429501296581</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6842028388645938</v>
+        <v>0.7118667611326142</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6860990217190243</v>
+        <v>0.7149450480415185</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6860990217190243</v>
+        <v>0.7149450480415185</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6804136142648234</v>
+        <v>0.7123014557295575</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6800581454193904</v>
+        <v>0.7083558736994936</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6804532271405785</v>
+        <v>0.7102103496054417</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6804532271405785</v>
+        <v>0.7096568163812329</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6841653200615657</v>
+        <v>0.709340960411555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6803760954617954</v>
+        <v>0.7070132240692719</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6677169023080172</v>
+        <v>0.6993086069879206</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6700852985624191</v>
+        <v>0.7008482739605546</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6672446889080458</v>
+        <v>0.7010067254635753</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6624693305598504</v>
+        <v>0.6699174237321261</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6471967346425942</v>
+        <v>0.6641402260900522</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6455382290426946</v>
+        <v>0.6680076294049693</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6435670085822081</v>
+        <v>0.6687550388624997</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6446719809578987</v>
+        <v>0.6669401758323067</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6504355671272464</v>
+        <v>0.669187639386716</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6504355671272464</v>
+        <v>0.6682004586019272</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6387145185552294</v>
+        <v>0.6691677456958081</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.627823246301344</v>
+        <v>0.6717321122562587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6390699874006625</v>
+        <v>0.6702716710351351</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6412799321520437</v>
+        <v>0.6750887363318128</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6415561752459663</v>
+        <v>0.6673143168262234</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6198518094533423</v>
+        <v>0.660518701814514</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6219825284532132</v>
+        <v>0.660518701814514</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6217062853592905</v>
+        <v>0.672907934092551</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.63836009674616</v>
+        <v>0.6722772691895589</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6436483284064456</v>
+        <v>0.6733040628501028</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6408848504308554</v>
+        <v>0.678239966774046</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.645106675554842</v>
+        <v>0.670700083413897</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6459343578002463</v>
+        <v>0.6575978193722668</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6515373983938462</v>
+        <v>0.6269952150438185</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6530364054543614</v>
+        <v>0.627432003713489</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6500352502242402</v>
+        <v>0.6271557606195663</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6511798354756861</v>
+        <v>0.6271547135832027</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6529165197907323</v>
+        <v>0.6240305315803618</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6330666299040566</v>
+        <v>0.6228046265046785</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6343269126736771</v>
+        <v>0.5563403286996158</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6287207309709867</v>
+        <v>0.5571711520541108</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6262366371984099</v>
+        <v>0.5590277220327862</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6124244825022773</v>
+        <v>0.5404808689005769</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6133720504113108</v>
+        <v>0.5413888239338552</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6068985735874607</v>
+        <v>0.5339302603979436</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6212860747653766</v>
+        <v>0.5487337840243192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6341307678615679</v>
+        <v>0.5489704142424867</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6251731972651411</v>
+        <v>0.5489704142424867</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6239097733864297</v>
+        <v>0.5529170433089141</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6235543045409967</v>
+        <v>0.5436425697064459</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6150637121627234</v>
+        <v>0.5368104829280721</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6184171951291868</v>
+        <v>0.5226856133713524</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6015340827786949</v>
+        <v>0.5329983980343638</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.600744966372682</v>
+        <v>0.5313419865071913</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5984537017970634</v>
+        <v>0.5313419865071913</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5977448581789246</v>
+        <v>0.5269439102620034</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5927234462852895</v>
+        <v>0.5176277297110529</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5792885736921642</v>
+        <v>0.5147078943051693</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5912326410096223</v>
+        <v>0.5368199062553443</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5909167850399444</v>
+        <v>0.5495344178303312</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5909167850399444</v>
+        <v>0.5332140875252598</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5909167850399444</v>
+        <v>0.5392862004097402</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5947070566760784</v>
+        <v>0.5376662606492324</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5393153429218597</v>
+        <v>0.5488337759970404</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5445274899397257</v>
+        <v>0.536520628361423</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5683824684231283</v>
+        <v>0.536520628361423</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5636488170234153</v>
+        <v>0.5373107918037994</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5641283596779316</v>
+        <v>0.5412199020671988</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5741950907955033</v>
+        <v>0.5380217294946654</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5575756571025712</v>
+        <v>0.5365623353099054</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5625063258446966</v>
+        <v>0.5358013143796484</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5566999856905031</v>
+        <v>0.5347745207191046</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5529493269301242</v>
+        <v>0.5334725310010017</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5465133689093022</v>
+        <v>0.5331566750313238</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5434308938549436</v>
+        <v>0.5331170621555686</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5434308938549436</v>
+        <v>0.5207131713684416</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5320600789465418</v>
+        <v>0.5225269873622711</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5344670410403354</v>
+        <v>0.5163203303050715</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5344670410403354</v>
+        <v>0.5204650237502748</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.513705007974927</v>
+        <v>0.5157324193869253</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5055218952754229</v>
+        <v>0.5117461774447426</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5021287994332043</v>
+        <v>0.5109497317841849</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.491712881688381</v>
+        <v>0.5109497317841849</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4912781870914377</v>
+        <v>0.5125258705234833</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4877182634552898</v>
+        <v>0.5067622843541356</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4915074880550602</v>
+        <v>0.5065652670117233</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4881102040673873</v>
+        <v>0.5031721711695047</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4883874941976735</v>
+        <v>0.5086532320267483</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.489335062106707</v>
+        <v>0.5086917978661399</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4921360588853251</v>
+        <v>0.5103096435539206</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4893736279460986</v>
+        <v>0.5078620215480083</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4877610174401357</v>
+        <v>0.5084145077358536</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4889056026915815</v>
+        <v>0.5067570491723178</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4855510726887545</v>
+        <v>0.5070729051419955</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4771220809498714</v>
+        <v>0.5070729051419955</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4734902608167582</v>
+        <v>0.5073887611116734</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4812229733738653</v>
+        <v>0.5069155006753384</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4897062364975936</v>
+        <v>0.5066392575814158</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4996279530788104</v>
+        <v>0.5037569409785602</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4972981226638001</v>
+        <v>0.5024549512604572</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4971417652335066</v>
+        <v>0.5030074374483026</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4936298307640224</v>
+        <v>0.5031658889513233</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.50437521595125</v>
+        <v>0.4978380444152825</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5052039452330179</v>
+        <v>0.496259811603257</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5046514590451726</v>
+        <v>0.4914437933429428</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5123560761265239</v>
+        <v>0.4917565082035299</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5181582281352631</v>
+        <v>0.4905764982217832</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5181582281352631</v>
+        <v>0.4578662096934626</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5156303333414769</v>
+        <v>0.45758996659954</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.527273203198347</v>
+        <v>0.4564891823693037</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5175181399049988</v>
+        <v>0.4560148748966052</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5186210182079624</v>
+        <v>0.4555405674239066</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5197656034594081</v>
+        <v>0.4555405674239066</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5190202880746049</v>
+        <v>0.4558564233935845</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.515417610453611</v>
+        <v>0.446504818112333</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5054592475996691</v>
+        <v>0.4562515051147726</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5009173783605505</v>
+        <v>0.4562515051147726</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4968466754850396</v>
+        <v>0.4562515051147726</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4974783874243952</v>
+        <v>0.4561337135238707</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4994881737242735</v>
+        <v>0.4698259825563742</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.499607012351539</v>
+        <v>0.497208426548654</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003169030060414</v>
+        <v>0.497208426548654</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5010267936605438</v>
+        <v>0.4995778698394195</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5007505505666212</v>
+        <v>0.5020244448089682</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5001188386272655</v>
+        <v>0.5013156011908293</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5001188386272655</v>
+        <v>0.5089336632661252</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5009871807847887</v>
+        <v>0.5101178613933262</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5004346945969433</v>
+        <v>0.5122881932689523</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5007505505666212</v>
+        <v>0.5122881932689523</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5004743074726985</v>
+        <v>0.5036881855906856</v>
       </c>
     </row>
   </sheetData>
